--- a/data/fmsForecastOutput/File1/RPT_RPT9892372453518NR_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT9892372453518NR_fmsForecastOutput.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1875,13 +1875,13 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>168.8311543927491</v>
+        <v>168.831154392749</v>
       </c>
       <c r="D8" s="149" t="n">
         <v>171.6192926502704</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>186.1133617763841</v>
+        <v>186.113361776384</v>
       </c>
       <c r="F8" s="149" t="n">
         <v>186.8670719411977</v>
@@ -1902,22 +1902,22 @@
         <v>100.0144596206879</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>98.37072929686119</v>
+        <v>98.37072929686116</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>25738.41694166522</v>
+        <v>25738.41694166521</v>
       </c>
       <c r="N8" s="152" t="n">
         <v>23878.37006924578</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>25281.1803768556</v>
+        <v>25281.18037685559</v>
       </c>
       <c r="P8" s="152" t="n">
         <v>24403.3529981302</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>24657.8453057521</v>
+        <v>24657.84530575209</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>181.1736063235402</v>
+        <v>181.1736063235401</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>184.1655722605182</v>
+        <v>184.1655722605181</v>
       </c>
       <c r="V8" s="149" t="n">
         <v>199.7192346359587</v>
@@ -1940,7 +1940,7 @@
         <v>213.9634485746926</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>163.3823689554769</v>
+        <v>163.3823689554768</v>
       </c>
       <c r="Z8" s="149" t="n">
         <v>130.1027599816049</v>
@@ -1955,19 +1955,19 @@
         <v>101.7920111315501</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>25738.41694166522</v>
+        <v>25738.41694166521</v>
       </c>
       <c r="AE8" s="152" t="n">
         <v>23878.37006924578</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>25281.1803768556</v>
+        <v>25281.18037685559</v>
       </c>
       <c r="AG8" s="152" t="n">
         <v>24403.3529981302</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>24657.8453057521</v>
+        <v>24657.84530575209</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>295.4733399463256</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>325.496709462285</v>
+        <v>325.4967094622849</v>
       </c>
       <c r="G9" s="157" t="n">
         <v>348.9888334192067</v>
@@ -2046,7 +2046,7 @@
         <v>162.7879524735079</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>175.1737350997654</v>
+        <v>175.1737350997653</v>
       </c>
       <c r="L9" s="157" t="n">
         <v>184.9182253190964</v>
@@ -2081,13 +2081,13 @@
         <v>297.601781808558</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>327.8414246320673</v>
+        <v>327.8414246320672</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>351.5027740767159</v>
+        <v>351.5027740767158</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>202.9296303802722</v>
+        <v>202.9296303802721</v>
       </c>
       <c r="Z9" s="156" t="n">
         <v>164.3199095249776</v>
@@ -2096,10 +2096,10 @@
         <v>163.4319246736625</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>175.8505851577324</v>
+        <v>175.8505851577323</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>185.6216589052937</v>
+        <v>185.6216589052936</v>
       </c>
       <c r="AD9" s="158" t="n">
         <v>21920.16704500929</v>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>203.5272933931917</v>
+        <v>203.5272933931916</v>
       </c>
       <c r="D10" s="162" t="n">
         <v>205.4251686871783</v>
@@ -2179,7 +2179,7 @@
         <v>227.4317781554929</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>241.8545153418868</v>
+        <v>241.8545153418867</v>
       </c>
       <c r="G10" s="163" t="n">
         <v>261.9310829378509</v>
@@ -2188,7 +2188,7 @@
         <v>172.3491162682639</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>139.6995694680196</v>
+        <v>139.6995694680195</v>
       </c>
       <c r="J10" s="162" t="n">
         <v>129.8478867266897</v>
@@ -2200,19 +2200,19 @@
         <v>133.0600198382123</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>47658.58398667451</v>
+        <v>47658.58398667449</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>45004.6094059863</v>
+        <v>45004.60940598629</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>49654.09622186436</v>
+        <v>49654.09622186435</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>52348.18063108556</v>
+        <v>52348.18063108555</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>55663.92671059562</v>
+        <v>55663.9267105956</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,22 +2220,22 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>213.5308143211516</v>
+        <v>213.5308143211515</v>
       </c>
       <c r="U10" s="162" t="n">
         <v>215.3022297036462</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>238.1704445553959</v>
+        <v>238.1704445553958</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>252.97003181205</v>
+        <v>252.9700318120499</v>
       </c>
       <c r="X10" s="163" t="n">
         <v>273.5955661477935</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>179.4689193169638</v>
+        <v>179.4689193169637</v>
       </c>
       <c r="Z10" s="162" t="n">
         <v>144.1982014686534</v>
@@ -2247,22 +2247,22 @@
         <v>132.8586804826105</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>136.0056203622418</v>
+        <v>136.0056203622417</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>47658.58398667451</v>
+        <v>47658.58398667449</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>45004.6094059863</v>
+        <v>45004.60940598629</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>49654.09622186436</v>
+        <v>49654.09622186435</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>52348.18063108556</v>
+        <v>52348.18063108555</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>55663.92671059562</v>
+        <v>55663.9267105956</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2330,7 +2330,7 @@
         <v>904.7079682969697</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>990.8838627148774</v>
+        <v>990.8838627148776</v>
       </c>
       <c r="H11" s="155" t="n">
         <v>466.7798249502652</v>
@@ -2345,7 +2345,7 @@
         <v>532.499701039077</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>551.8129773959415</v>
+        <v>551.8129773959416</v>
       </c>
       <c r="M11" s="158" t="n">
         <v>43344.70295646971</v>
@@ -2360,7 +2360,7 @@
         <v>72973.76092180275</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>83935.06476980842</v>
+        <v>83935.06476980844</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>601.5151907494834</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>619.0110084810206</v>
+        <v>619.0110084810207</v>
       </c>
       <c r="AD11" s="158" t="n">
         <v>43344.70295646971</v>
@@ -2410,7 +2410,7 @@
         <v>72973.76092180275</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>83935.06476980842</v>
+        <v>83935.06476980844</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>292.9334129257201</v>
+        <v>292.93341292572</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>313.8053478557997</v>
+        <v>313.8053478557996</v>
       </c>
       <c r="E12" s="162" t="n">
         <v>362.9989687572867</v>
@@ -2476,7 +2476,7 @@
         <v>469.6809338134883</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>246.3659891868345</v>
+        <v>246.3659891868344</v>
       </c>
       <c r="I12" s="162" t="n">
         <v>217.9181417806051</v>
@@ -2488,13 +2488,13 @@
         <v>231.8352693063713</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>244.7195480522159</v>
+        <v>244.719548052216</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>91003.28694314421</v>
+        <v>91003.28694314418</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>93678.62704280759</v>
+        <v>93678.62704280758</v>
       </c>
       <c r="O12" s="165" t="n">
         <v>109089.8541592967</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>319.5568689679961</v>
+        <v>319.556868967996</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>343.1604862544158</v>
+        <v>343.1604862544157</v>
       </c>
       <c r="V12" s="162" t="n">
         <v>397.1863209141924</v>
@@ -2541,10 +2541,10 @@
         <v>256.2050661292249</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>91003.28694314421</v>
+        <v>91003.28694314418</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>93678.62704280759</v>
+        <v>93678.62704280758</v>
       </c>
       <c r="AF12" s="165" t="n">
         <v>109089.8541592967</v>
@@ -2606,43 +2606,43 @@
         <v>245.5649990194621</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>362.5762081422322</v>
+        <v>362.576208142232</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>392.6941139741027</v>
+        <v>392.6941139741026</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>417.8253527933692</v>
+        <v>417.8253527933691</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>447.7903039096205</v>
+        <v>447.7903039096203</v>
       </c>
       <c r="H13" s="155" t="n">
         <v>245.5649990194621</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>362.5762081422322</v>
+        <v>362.576208142232</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>392.6941139741027</v>
+        <v>392.6941139741026</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>417.8253527933692</v>
+        <v>417.8253527933691</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>447.7903039096205</v>
+        <v>447.7903039096203</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>736.4368637819756</v>
+        <v>736.4368637819755</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>805.1896113223746</v>
+        <v>805.1896113223744</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>898.5758174492479</v>
+        <v>898.5758174492477</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>975.4712887117287</v>
+        <v>975.4712887117284</v>
       </c>
       <c r="Q13" s="160" t="n">
         <v>1066.629990298585</v>
@@ -2656,43 +2656,43 @@
         <v>40.92749983657703</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>60.42936802370537</v>
+        <v>60.42936802370534</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>65.44901899568379</v>
+        <v>65.44901899568377</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>69.63755879889489</v>
+        <v>69.63755879889486</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>74.63171731827009</v>
+        <v>74.63171731827006</v>
       </c>
       <c r="Y13" s="155" t="n">
         <v>40.92749983657703</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>60.42936802370537</v>
+        <v>60.42936802370534</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>65.44901899568379</v>
+        <v>65.44901899568377</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>69.63755879889489</v>
+        <v>69.63755879889486</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>74.63171731827009</v>
+        <v>74.63171731827006</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>736.4368637819756</v>
+        <v>736.4368637819755</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>805.1896113223746</v>
+        <v>805.1896113223744</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>898.5758174492479</v>
+        <v>898.5758174492477</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>975.4712887117287</v>
+        <v>975.4712887117284</v>
       </c>
       <c r="AH13" s="160" t="n">
         <v>1066.629990298585</v>
@@ -2749,10 +2749,10 @@
         <v>292.480518044717</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>314.1654786926691</v>
+        <v>314.165478692669</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>363.2233634397903</v>
+        <v>363.2233634397902</v>
       </c>
       <c r="F14" s="168" t="n">
         <v>421.7792960375185</v>
@@ -2761,10 +2761,10 @@
         <v>469.5068928948636</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>246.3595384668183</v>
+        <v>246.3595384668182</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>218.6616000720949</v>
+        <v>218.6616000720948</v>
       </c>
       <c r="J14" s="168" t="n">
         <v>215.3667414815024</v>
@@ -2776,10 +2776,10 @@
         <v>245.5639771297504</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>91739.72380692619</v>
+        <v>91739.72380692617</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>94483.81665412997</v>
+        <v>94483.81665412996</v>
       </c>
       <c r="O14" s="171" t="n">
         <v>109988.4299767459</v>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>302.9980412125122</v>
+        <v>302.9980412125121</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>330.0026720504128</v>
+        <v>330.0026720504127</v>
       </c>
       <c r="V14" s="168" t="n">
         <v>381.3930646596941</v>
@@ -2814,7 +2814,7 @@
         <v>253.7795172218292</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>226.2177668207591</v>
+        <v>226.217766820759</v>
       </c>
       <c r="AA14" s="168" t="n">
         <v>221.6271521352696</v>
@@ -2826,10 +2826,10 @@
         <v>251.5641550335367</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>91739.72380692619</v>
+        <v>91739.72380692617</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>94483.81665412997</v>
+        <v>94483.81665412996</v>
       </c>
       <c r="AF14" s="171" t="n">
         <v>109988.4299767459</v>
@@ -3718,7 +3718,7 @@
         <v>297.2209034481251</v>
       </c>
       <c r="H23" s="85" t="n">
-        <v>58.72048393034001</v>
+        <v>58.72048393034</v>
       </c>
       <c r="I23" s="86" t="n">
         <v>131.35525567278</v>
@@ -3745,7 +3745,7 @@
         <v>540.5646083438444</v>
       </c>
       <c r="Q23" s="87" t="n">
-        <v>570.4447911558651</v>
+        <v>570.444791155865</v>
       </c>
       <c r="S23" s="42" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>271.6482086542927</v>
       </c>
       <c r="Y23" s="85" t="n">
-        <v>58.72048393034001</v>
+        <v>58.72048393034</v>
       </c>
       <c r="Z23" s="86" t="n">
         <v>131.35525567278</v>
@@ -3852,7 +3852,7 @@
         <v>2.334638820239654</v>
       </c>
       <c r="G24" s="81" t="n">
-        <v>2.381985453874114</v>
+        <v>2.381985453874115</v>
       </c>
       <c r="H24" s="79" t="n">
         <v>0</v>
@@ -3882,7 +3882,7 @@
         <v>2.334638820239654</v>
       </c>
       <c r="Q24" s="81" t="n">
-        <v>2.381985453874114</v>
+        <v>2.381985453874115</v>
       </c>
       <c r="S24" s="32" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>14.00783292143792</v>
       </c>
       <c r="X24" s="81" t="n">
-        <v>14.29191272324468</v>
+        <v>14.29191272324469</v>
       </c>
       <c r="Y24" s="79" t="n">
         <v>0</v>
@@ -3932,7 +3932,7 @@
         <v>14.00783292143792</v>
       </c>
       <c r="AH24" s="81" t="n">
-        <v>14.29191272324468</v>
+        <v>14.29191272324469</v>
       </c>
     </row>
     <row r="25" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -3945,7 +3945,7 @@
         <v>313.660972772553</v>
       </c>
       <c r="D25" s="92" t="n">
-        <v>300.7453812153509</v>
+        <v>300.745381215351</v>
       </c>
       <c r="E25" s="92" t="n">
         <v>302.8121014439594</v>
@@ -3957,7 +3957,7 @@
         <v>299.6028889019992</v>
       </c>
       <c r="H25" s="91" t="n">
-        <v>58.72048393034001</v>
+        <v>58.72048393034</v>
       </c>
       <c r="I25" s="92" t="n">
         <v>131.35525567278</v>
@@ -4007,7 +4007,7 @@
         <v>285.9401213775374</v>
       </c>
       <c r="Y25" s="91" t="n">
-        <v>58.72048393034001</v>
+        <v>58.72048393034</v>
       </c>
       <c r="Z25" s="92" t="n">
         <v>131.35525567278</v>
@@ -4028,7 +4028,7 @@
         <v>417.6675332888115</v>
       </c>
       <c r="AF25" s="92" t="n">
-        <v>496.2768727435289</v>
+        <v>496.2768727435288</v>
       </c>
       <c r="AG25" s="92" t="n">
         <v>529.3384086374205</v>
@@ -4408,13 +4408,13 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>171.8792907918565</v>
+        <v>171.8792907918564</v>
       </c>
       <c r="D35" s="149" t="n">
         <v>179.2220110803922</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>195.907882372609</v>
+        <v>195.9078823726089</v>
       </c>
       <c r="F35" s="149" t="n">
         <v>199.3146296083648</v>
@@ -4423,7 +4423,7 @@
         <v>213.1926627868784</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>156.0446733835886</v>
+        <v>156.0446733835885</v>
       </c>
       <c r="I35" s="149" t="n">
         <v>129.1940920210261</v>
@@ -4435,22 +4435,22 @@
         <v>106.6766058230473</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>105.1818718247416</v>
+        <v>105.1818718247415</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>26203.1072757299</v>
+        <v>26203.10727572989</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>24936.17960454477</v>
+        <v>24936.17960454476</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>26611.64391549987</v>
+        <v>26611.64391549986</v>
       </c>
       <c r="P35" s="152" t="n">
         <v>26028.90500448929</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>26365.14279158321</v>
+        <v>26365.1427915832</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4458,19 +4458,19 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>184.4445776438433</v>
+        <v>184.4445776438432</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>192.3240896905617</v>
+        <v>192.3240896905616</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>210.2297865836179</v>
+        <v>210.2297865836178</v>
       </c>
       <c r="W35" s="149" t="n">
         <v>213.8855850928127</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>228.7781760288434</v>
+        <v>228.7781760288433</v>
       </c>
       <c r="Y35" s="148" t="n">
         <v>166.332131086624</v>
@@ -4488,19 +4488,19 @@
         <v>108.840041587076</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>26203.1072757299</v>
+        <v>26203.10727572989</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>24936.17960454477</v>
+        <v>24936.17960454476</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>26611.64391549987</v>
+        <v>26611.64391549986</v>
       </c>
       <c r="AG35" s="152" t="n">
         <v>26028.90500448929</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>26365.14279158321</v>
+        <v>26365.1427915832</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4519,7 +4519,7 @@
         <v>310.485521541103</v>
       </c>
       <c r="F36" s="156" t="n">
-        <v>346.3989019796252</v>
+        <v>346.3989019796251</v>
       </c>
       <c r="G36" s="157" t="n">
         <v>372.3484651943247</v>
@@ -4537,7 +4537,7 @@
         <v>186.4227432420769</v>
       </c>
       <c r="L36" s="157" t="n">
-        <v>197.2957607538008</v>
+        <v>197.2957607538007</v>
       </c>
       <c r="M36" s="158" t="n">
         <v>22253.17409061121</v>
@@ -4549,10 +4549,10 @@
         <v>25611.23615751466</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>29739.34091087101</v>
+        <v>29739.340910871</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>33081.47916846323</v>
+        <v>33081.47916846322</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>274.2968587212048</v>
+        <v>274.2968587212047</v>
       </c>
       <c r="U36" s="156" t="n">
         <v>277.8993739455734</v>
@@ -4572,7 +4572,7 @@
         <v>348.8941860690076</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>375.0306769322823</v>
+        <v>375.0306769322822</v>
       </c>
       <c r="Y36" s="155" t="n">
         <v>206.0124990709745</v>
@@ -4599,10 +4599,10 @@
         <v>25611.23615751466</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>29739.34091087101</v>
+        <v>29739.340910871</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>33081.47916846323</v>
+        <v>33081.47916846322</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,16 +4612,16 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>206.9338819875104</v>
+        <v>206.9338819875103</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>214.5051045459706</v>
+        <v>214.5051045459705</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>239.1976368341762</v>
+        <v>239.1976368341761</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>257.6556037807597</v>
+        <v>257.6556037807596</v>
       </c>
       <c r="G37" s="163" t="n">
         <v>279.7308595914789</v>
@@ -4636,25 +4636,25 @@
         <v>136.5653819568742</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>138.2028388185149</v>
+        <v>138.2028388185148</v>
       </c>
       <c r="L37" s="163" t="n">
         <v>142.1022404409861</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>48456.28136634112</v>
+        <v>48456.28136634111</v>
       </c>
       <c r="N37" s="165" t="n">
         <v>46993.84455846476</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>52222.88007301453</v>
+        <v>52222.88007301452</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>55768.2459153603</v>
+        <v>55768.24591536028</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>59446.62196004644</v>
+        <v>59446.62196004642</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4662,13 +4662,13 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>217.1048393301549</v>
+        <v>217.1048393301548</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>224.8187385543267</v>
+        <v>224.8187385543266</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>250.4918528247455</v>
+        <v>250.4918528247454</v>
       </c>
       <c r="W37" s="162" t="n">
         <v>269.4973306280189</v>
@@ -4677,34 +4677,34 @@
         <v>292.188013887221</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>182.4728249032223</v>
+        <v>182.4728249032222</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>150.5718626351797</v>
+        <v>150.5718626351796</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>140.1737677970666</v>
+        <v>140.1737677970665</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>141.5387407130763</v>
+        <v>141.5387407130762</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>145.24801205907</v>
+        <v>145.2480120590699</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>48456.28136634112</v>
+        <v>48456.28136634111</v>
       </c>
       <c r="AE37" s="165" t="n">
         <v>46993.84455846476</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>52222.88007301453</v>
+        <v>52222.88007301452</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>55768.2459153603</v>
+        <v>55768.24591536028</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>59446.62196004644</v>
+        <v>59446.62196004642</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4741,7 +4741,7 @@
         <v>566.8663642518962</v>
       </c>
       <c r="L38" s="157" t="n">
-        <v>588.0672647234338</v>
+        <v>588.0672647234339</v>
       </c>
       <c r="M38" s="158" t="n">
         <v>44304.72287151826</v>
@@ -4756,7 +4756,7 @@
         <v>77683.36857055586</v>
       </c>
       <c r="Q38" s="160" t="n">
-        <v>89449.62510033298</v>
+        <v>89449.625100333</v>
       </c>
       <c r="S38" s="32" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>640.3360012354696</v>
       </c>
       <c r="AC38" s="157" t="n">
-        <v>659.6802277267453</v>
+        <v>659.6802277267454</v>
       </c>
       <c r="AD38" s="158" t="n">
         <v>44304.72287151826</v>
@@ -4806,7 +4806,7 @@
         <v>77683.36857055586</v>
       </c>
       <c r="AH38" s="160" t="n">
-        <v>89449.62510033298</v>
+        <v>89449.625100333</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" thickTop="1">
@@ -4816,10 +4816,10 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>298.5913857681865</v>
+        <v>298.5913857681864</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>327.9192301145427</v>
+        <v>327.9192301145426</v>
       </c>
       <c r="E39" s="162" t="n">
         <v>381.8368663797842</v>
@@ -4831,7 +4831,7 @@
         <v>500.9615586689944</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>251.1245179671615</v>
+        <v>251.1245179671614</v>
       </c>
       <c r="I39" s="162" t="n">
         <v>227.7193482168602</v>
@@ -4843,13 +4843,13 @@
         <v>246.8744946044077</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>261.0178046479801</v>
+        <v>261.0178046479802</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>92761.00423785939</v>
+        <v>92761.00423785936</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>97891.96859761899</v>
+        <v>97891.96859761898</v>
       </c>
       <c r="O39" s="165" t="n">
         <v>114751.0920171928</v>
@@ -4866,7 +4866,7 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>325.7290705894716</v>
+        <v>325.7290705894715</v>
       </c>
       <c r="U39" s="162" t="n">
         <v>358.5946613949664</v>
@@ -4896,10 +4896,10 @@
         <v>273.2682551639557</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>92761.00423785939</v>
+        <v>92761.00423785936</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>97891.96859761899</v>
+        <v>97891.96859761898</v>
       </c>
       <c r="AF39" s="165" t="n">
         <v>114751.0920171928</v>
@@ -4918,46 +4918,46 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>229.300384964129</v>
+        <v>229.3003849641289</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>347.2212936759051</v>
+        <v>347.221293675905</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>379.891773714928</v>
+        <v>379.8917737149279</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>410.1189307766605</v>
+        <v>410.1189307766604</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>441.6747640809031</v>
+        <v>441.6747640809029</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>229.300384964129</v>
+        <v>229.3003849641289</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>347.2212936759051</v>
+        <v>347.221293675905</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>379.891773714928</v>
+        <v>379.8917737149279</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>410.1189307766605</v>
+        <v>410.1189307766604</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>441.6747640809031</v>
+        <v>441.6747640809029</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>687.6601186702486</v>
+        <v>687.6601186702485</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>771.0902486687166</v>
+        <v>771.0902486687164</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>869.281073896229</v>
+        <v>869.2810738962288</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>957.4795767063711</v>
+        <v>957.4795767063708</v>
       </c>
       <c r="Q40" s="160" t="n">
         <v>1052.062863383992</v>
@@ -4968,46 +4968,46 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>38.21673082735484</v>
+        <v>38.21673082735483</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>57.87021561265087</v>
+        <v>57.87021561265084</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>63.31529561915468</v>
+        <v>63.31529561915466</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>68.35315512944344</v>
+        <v>68.35315512944341</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>73.61246068015052</v>
+        <v>73.61246068015049</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>38.21673082735484</v>
+        <v>38.21673082735483</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>57.87021561265087</v>
+        <v>57.87021561265084</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>63.31529561915468</v>
+        <v>63.31529561915466</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>68.35315512944344</v>
+        <v>68.35315512944341</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>73.61246068015052</v>
+        <v>73.61246068015049</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>687.6601186702486</v>
+        <v>687.6601186702485</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>771.0902486687166</v>
+        <v>771.0902486687164</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>869.281073896229</v>
+        <v>869.2810738962288</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>957.4795767063711</v>
+        <v>957.4795767063708</v>
       </c>
       <c r="AH40" s="160" t="n">
         <v>1052.062863383992</v>
@@ -5023,7 +5023,7 @@
         <v>297.9288864996687</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>328.0617592449053</v>
+        <v>328.0617592449052</v>
       </c>
       <c r="E41" s="180" t="n">
         <v>381.8221680697479</v>
@@ -5050,7 +5050,7 @@
         <v>261.7690304409803</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>93448.66435652964</v>
+        <v>93448.66435652963</v>
       </c>
       <c r="N41" s="183" t="n">
         <v>98663.05884628771</v>
@@ -5100,7 +5100,7 @@
         <v>268.1651670840906</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>93448.66435652964</v>
+        <v>93448.66435652963</v>
       </c>
       <c r="AE41" s="189" t="n">
         <v>98663.05884628771</v>
@@ -6334,7 +6334,7 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.06214434575962197</v>
+        <v>0.06214434575962194</v>
       </c>
       <c r="D57" s="149" t="n">
         <v>0</v>
@@ -6349,7 +6349,7 @@
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.05641921194822884</v>
+        <v>0.05641921194822882</v>
       </c>
       <c r="I57" s="149" t="n">
         <v>0</v>
@@ -6364,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>9.473945063523479</v>
+        <v>9.473945063523475</v>
       </c>
       <c r="N57" s="152" t="n">
         <v>0</v>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.06668742670381968</v>
+        <v>0.06668742670381965</v>
       </c>
       <c r="U57" s="149" t="n">
         <v>0</v>
@@ -6399,7 +6399,7 @@
         <v>0</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.06013872536685886</v>
+        <v>0.06013872536685884</v>
       </c>
       <c r="Z57" s="149" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
         <v>0</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>9.473945063523479</v>
+        <v>9.473945063523475</v>
       </c>
       <c r="AE57" s="152" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.1871623796096994</v>
+        <v>0.1871623796096995</v>
       </c>
       <c r="Z61" s="162" t="n">
         <v>0</v>
@@ -7297,43 +7297,43 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.8434271547878568</v>
+        <v>0.8434271547878563</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.5076327417923732</v>
+        <v>0.5076327417923731</v>
       </c>
       <c r="E68" s="149" t="n">
         <v>0.2386522012331492</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.1110105443255848</v>
+        <v>0.1110105443255847</v>
       </c>
       <c r="G68" s="150" t="n">
         <v>0.1289246844412498</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.7657252615214785</v>
+        <v>0.7657252615214781</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.3659324586341772</v>
+        <v>0.3659324586341771</v>
       </c>
       <c r="J68" s="149" t="n">
         <v>0.1393239773741763</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.059414745934562</v>
+        <v>0.05941474593456197</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.06360697153776257</v>
+        <v>0.06360697153776255</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>128.5810065561253</v>
+        <v>128.5810065561252</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>70.62983584535287</v>
+        <v>70.62983584535286</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>32.41792684373758</v>
+        <v>32.41792684373759</v>
       </c>
       <c r="P68" s="152" t="n">
         <v>14.4970939585562</v>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.9050861486657081</v>
+        <v>0.9050861486657077</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.5447433848878583</v>
+        <v>0.5447433848878582</v>
       </c>
       <c r="V68" s="149" t="n">
         <v>0.2560989416318167</v>
@@ -7362,28 +7362,28 @@
         <v>0.1383497619758549</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.816206742684785</v>
+        <v>0.8162067426847847</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.3848309810879126</v>
+        <v>0.3848309810879125</v>
       </c>
       <c r="AA68" s="149" t="n">
         <v>0.1450945378717719</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.0616630848367926</v>
+        <v>0.06166308483679258</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.06581918830017978</v>
+        <v>0.06581918830017977</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>128.5810065561253</v>
+        <v>128.5810065561252</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>70.62983584535287</v>
+        <v>70.62983584535286</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>32.41792684373758</v>
+        <v>32.41792684373759</v>
       </c>
       <c r="AG68" s="152" t="n">
         <v>14.4970939585562</v>
@@ -7426,7 +7426,7 @@
         <v>0.5185172297128533</v>
       </c>
       <c r="L69" s="157" t="n">
-        <v>0.5402681549517188</v>
+        <v>0.5402681549517186</v>
       </c>
       <c r="M69" s="158" t="n">
         <v>124.7760115321655</v>
@@ -7441,7 +7441,7 @@
         <v>82.71716419582476</v>
       </c>
       <c r="Q69" s="160" t="n">
-        <v>90.58922323081408</v>
+        <v>90.58922323081407</v>
       </c>
       <c r="S69" s="32" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>0.5205207173749058</v>
       </c>
       <c r="AC69" s="157" t="n">
-        <v>0.5423233486195688</v>
+        <v>0.5423233486195687</v>
       </c>
       <c r="AD69" s="158" t="n">
         <v>124.7760115321655</v>
@@ -7491,7 +7491,7 @@
         <v>82.71716419582476</v>
       </c>
       <c r="AH69" s="160" t="n">
-        <v>90.58922323081408</v>
+        <v>90.58922323081407</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" thickTop="1">
@@ -7501,22 +7501,22 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>1.081968112357209</v>
+        <v>1.081968112357208</v>
       </c>
       <c r="D70" s="162" t="n">
         <v>0.6280312203044942</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.4940008408570774</v>
+        <v>0.4940008408570775</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.449140868064612</v>
+        <v>0.4491408680646118</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.5013000718939864</v>
+        <v>0.5013000718939863</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.9162223153774058</v>
+        <v>0.9162223153774055</v>
       </c>
       <c r="I70" s="162" t="n">
         <v>0.4270931923761338</v>
@@ -7525,13 +7525,13 @@
         <v>0.2820404683405499</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.2409128390188603</v>
+        <v>0.2409128390188602</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>0.254658579512451</v>
+        <v>0.2546585795124509</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>253.3570180882908</v>
+        <v>253.3570180882907</v>
       </c>
       <c r="N70" s="165" t="n">
         <v>137.5892737253126</v>
@@ -7540,10 +7540,10 @@
         <v>107.8528492567511</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>97.21425815438097</v>
+        <v>97.21425815438096</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>106.533100802489</v>
+        <v>106.5331008024889</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7551,37 +7551,37 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>1.135147666189534</v>
+        <v>1.135147666189533</v>
       </c>
       <c r="U70" s="162" t="n">
         <v>0.6582276306218704</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.517326122285466</v>
+        <v>0.5173261222854662</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.4697831649815757</v>
+        <v>0.4697831649815756</v>
       </c>
       <c r="X70" s="163" t="n">
         <v>0.5236242886542319</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.9540717838026296</v>
+        <v>0.9540717838026292</v>
       </c>
       <c r="Z70" s="162" t="n">
         <v>0.4408465282653755</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.2894926558403266</v>
+        <v>0.2894926558403267</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.2467279264872338</v>
+        <v>0.2467279264872337</v>
       </c>
       <c r="AC70" s="163" t="n">
         <v>0.260296053835486</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>253.3570180882908</v>
+        <v>253.3570180882907</v>
       </c>
       <c r="AE70" s="165" t="n">
         <v>137.5892737253126</v>
@@ -7590,10 +7590,10 @@
         <v>107.8528492567511</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>97.21425815438097</v>
+        <v>97.21425815438096</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>106.533100802489</v>
+        <v>106.5331008024889</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7615,7 +7615,7 @@
         <v>2.390163817245793</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>4.103085148771919</v>
+        <v>4.103085148771918</v>
       </c>
       <c r="H71" s="155" t="n">
         <v>0.5547423026400453</v>
@@ -7624,13 +7624,13 @@
         <v>0.7058546822306386</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>0.8851035230875919</v>
+        <v>0.8851035230875922</v>
       </c>
       <c r="K71" s="156" t="n">
         <v>1.406820280928509</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>2.284965693405785</v>
+        <v>2.284965693405784</v>
       </c>
       <c r="M71" s="158" t="n">
         <v>51.51280976610925</v>
@@ -7645,7 +7645,7 @@
         <v>192.7906562953858</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>347.5611327190496</v>
+        <v>347.5611327190495</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>2.968906547908312</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>5.096586383292905</v>
+        <v>5.096586383292903</v>
       </c>
       <c r="Y71" s="155" t="n">
         <v>0.6608722221628459</v>
@@ -7674,13 +7674,13 @@
         <v>0.8243619451887231</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>1.014046347476097</v>
+        <v>1.014046347476098</v>
       </c>
       <c r="AB71" s="156" t="n">
         <v>1.58915351122583</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>2.563221555416164</v>
+        <v>2.563221555416163</v>
       </c>
       <c r="AD71" s="158" t="n">
         <v>51.51280976610925</v>
@@ -7695,7 +7695,7 @@
         <v>192.7906562953858</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>347.5611327190496</v>
+        <v>347.5611327190495</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7705,13 +7705,13 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>0.9813553133224946</v>
+        <v>0.9813553133224944</v>
       </c>
       <c r="D72" s="162" t="n">
         <v>0.7156157657092143</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.7300156140825065</v>
+        <v>0.7300156140825067</v>
       </c>
       <c r="F72" s="162" t="n">
         <v>0.9761026487501236</v>
@@ -7720,13 +7720,13 @@
         <v>1.527800461722212</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.8253499322447014</v>
+        <v>0.8253499322447013</v>
       </c>
       <c r="I72" s="162" t="n">
         <v>0.4969502876793459</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.4315121284869896</v>
+        <v>0.4315121284869897</v>
       </c>
       <c r="K72" s="162" t="n">
         <v>0.5364852044943708</v>
@@ -7735,19 +7735,19 @@
         <v>0.7960353754855558</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>304.8698278544</v>
+        <v>304.8698278543999</v>
       </c>
       <c r="N72" s="165" t="n">
         <v>213.6289355165229</v>
       </c>
       <c r="O72" s="165" t="n">
-        <v>219.3871160210325</v>
+        <v>219.3871160210326</v>
       </c>
       <c r="P72" s="165" t="n">
         <v>290.0049144497668</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>454.0942335215386</v>
+        <v>454.0942335215385</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>0.7825585376733135</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.7987687043849908</v>
+        <v>0.798768704384991</v>
       </c>
       <c r="W72" s="162" t="n">
         <v>1.066700818068707</v>
@@ -7770,34 +7770,34 @@
         <v>1.671626092331173</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.8875392333071003</v>
+        <v>0.8875392333071002</v>
       </c>
       <c r="Z72" s="162" t="n">
         <v>0.5283358554219204</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.4546435921901261</v>
+        <v>0.4546435921901262</v>
       </c>
       <c r="AB72" s="162" t="n">
         <v>0.5627551092749425</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>0.83339601450213</v>
+        <v>0.8333960145021297</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>304.8698278544</v>
+        <v>304.8698278543999</v>
       </c>
       <c r="AE72" s="165" t="n">
         <v>213.6289355165229</v>
       </c>
       <c r="AF72" s="165" t="n">
-        <v>219.3871160210325</v>
+        <v>219.3871160210326</v>
       </c>
       <c r="AG72" s="165" t="n">
         <v>290.0049144497668</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>454.0942335215386</v>
+        <v>454.0942335215385</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7807,49 +7807,49 @@
         </is>
       </c>
       <c r="C73" s="155" t="n">
-        <v>22.52427460963667</v>
+        <v>22.52427460963666</v>
       </c>
       <c r="D73" s="156" t="n">
-        <v>32.52028395838352</v>
+        <v>32.52028395838351</v>
       </c>
       <c r="E73" s="156" t="n">
         <v>33.86831783406382</v>
       </c>
       <c r="F73" s="156" t="n">
-        <v>35.35776816236777</v>
+        <v>35.35776816236776</v>
       </c>
       <c r="G73" s="157" t="n">
-        <v>36.92500467223028</v>
+        <v>36.92500467223027</v>
       </c>
       <c r="H73" s="155" t="n">
-        <v>22.52427460963667</v>
+        <v>22.52427460963666</v>
       </c>
       <c r="I73" s="156" t="n">
-        <v>32.52028395838352</v>
+        <v>32.52028395838351</v>
       </c>
       <c r="J73" s="156" t="n">
         <v>33.86831783406382</v>
       </c>
       <c r="K73" s="156" t="n">
-        <v>35.35776816236777</v>
+        <v>35.35776816236776</v>
       </c>
       <c r="L73" s="157" t="n">
-        <v>36.92500467223028</v>
+        <v>36.92500467223027</v>
       </c>
       <c r="M73" s="158" t="n">
-        <v>67.54914673800951</v>
+        <v>67.5491467380095</v>
       </c>
       <c r="N73" s="159" t="n">
-        <v>72.21928580121335</v>
+        <v>72.21928580121333</v>
       </c>
       <c r="O73" s="159" t="n">
-        <v>77.49861864591595</v>
+        <v>77.49861864591594</v>
       </c>
       <c r="P73" s="159" t="n">
-        <v>82.54761814889748</v>
+        <v>82.54761814889747</v>
       </c>
       <c r="Q73" s="160" t="n">
-        <v>87.95482401348623</v>
+        <v>87.9548240134862</v>
       </c>
       <c r="S73" s="32" t="inlineStr">
         <is>
@@ -7857,49 +7857,49 @@
         </is>
       </c>
       <c r="T73" s="155" t="n">
-        <v>3.754045768272778</v>
+        <v>3.754045768272777</v>
       </c>
       <c r="U73" s="156" t="n">
-        <v>5.420047326397254</v>
+        <v>5.420047326397253</v>
       </c>
       <c r="V73" s="156" t="n">
-        <v>5.644719639010638</v>
+        <v>5.644719639010637</v>
       </c>
       <c r="W73" s="156" t="n">
         <v>5.892961360394628</v>
       </c>
       <c r="X73" s="157" t="n">
-        <v>6.154167445371714</v>
+        <v>6.154167445371711</v>
       </c>
       <c r="Y73" s="155" t="n">
-        <v>3.754045768272778</v>
+        <v>3.754045768272777</v>
       </c>
       <c r="Z73" s="156" t="n">
-        <v>5.420047326397254</v>
+        <v>5.420047326397253</v>
       </c>
       <c r="AA73" s="156" t="n">
-        <v>5.644719639010638</v>
+        <v>5.644719639010637</v>
       </c>
       <c r="AB73" s="156" t="n">
         <v>5.892961360394628</v>
       </c>
       <c r="AC73" s="157" t="n">
-        <v>6.154167445371714</v>
+        <v>6.154167445371711</v>
       </c>
       <c r="AD73" s="158" t="n">
-        <v>67.54914673800951</v>
+        <v>67.5491467380095</v>
       </c>
       <c r="AE73" s="159" t="n">
-        <v>72.21928580121335</v>
+        <v>72.21928580121333</v>
       </c>
       <c r="AF73" s="159" t="n">
-        <v>77.49861864591595</v>
+        <v>77.49861864591594</v>
       </c>
       <c r="AG73" s="159" t="n">
-        <v>82.54761814889748</v>
+        <v>82.54761814889747</v>
       </c>
       <c r="AH73" s="160" t="n">
-        <v>87.95482401348623</v>
+        <v>87.9548240134862</v>
       </c>
     </row>
     <row r="74" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -7912,16 +7912,16 @@
         <v>1.187329655010871</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.9504658730338159</v>
+        <v>0.9504658730338157</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>0.9804288971651031</v>
+        <v>0.9804288971651034</v>
       </c>
       <c r="F74" s="180" t="n">
         <v>1.244165984092921</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>1.809225069629854</v>
+        <v>1.809225069629853</v>
       </c>
       <c r="H74" s="179" t="n">
         <v>1.00010075122926</v>
@@ -7930,28 +7930,28 @@
         <v>0.6615315899007601</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.5813276294704893</v>
+        <v>0.5813276294704895</v>
       </c>
       <c r="K74" s="180" t="n">
         <v>0.6862277568899726</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.9462704602308021</v>
+        <v>0.9462704602308019</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>372.4189745924095</v>
+        <v>372.4189745924094</v>
       </c>
       <c r="N74" s="183" t="n">
         <v>285.8482213177363</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>296.8857346669485</v>
+        <v>296.8857346669486</v>
       </c>
       <c r="P74" s="183" t="n">
         <v>372.5525325986642</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>542.0490575350248</v>
+        <v>542.0490575350246</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>1.230025719821854</v>
+        <v>1.230025719821853</v>
       </c>
       <c r="U74" s="186" t="n">
         <v>0.9983791952543596</v>
@@ -7980,28 +7980,28 @@
         <v>0.6843917674589183</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.5982260124790787</v>
+        <v>0.598226012479079</v>
       </c>
       <c r="AB74" s="186" t="n">
         <v>0.7038078599995388</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.9693918934835405</v>
+        <v>0.9693918934835403</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>372.4189745924095</v>
+        <v>372.4189745924094</v>
       </c>
       <c r="AE74" s="189" t="n">
         <v>285.8482213177363</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>296.8857346669485</v>
+        <v>296.8857346669486</v>
       </c>
       <c r="AG74" s="189" t="n">
         <v>372.5525325986642</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>542.0490575350248</v>
+        <v>542.0490575350246</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,28 +8260,28 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>172.784862292404</v>
+        <v>172.7848622924039</v>
       </c>
       <c r="D79" s="149" t="n">
         <v>179.7296438221846</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>196.1465345738421</v>
+        <v>196.146534573842</v>
       </c>
       <c r="F79" s="149" t="n">
         <v>199.4256401526904</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>213.3215874713197</v>
+        <v>213.3215874713196</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>156.8668178570583</v>
+        <v>156.8668178570582</v>
       </c>
       <c r="I79" s="149" t="n">
         <v>129.5600244796603</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>114.5093789363011</v>
+        <v>114.509378936301</v>
       </c>
       <c r="K79" s="149" t="n">
         <v>106.7360205689818</v>
@@ -8290,19 +8290,19 @@
         <v>105.2454787962793</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>26341.16222734955</v>
+        <v>26341.16222734954</v>
       </c>
       <c r="N79" s="152" t="n">
         <v>25006.80944039012</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>26644.06184234361</v>
+        <v>26644.0618423436</v>
       </c>
       <c r="P79" s="152" t="n">
         <v>26043.40209844784</v>
       </c>
       <c r="Q79" s="153" t="n">
-        <v>26381.08666915488</v>
+        <v>26381.08666915487</v>
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
@@ -8310,13 +8310,13 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>185.4163512192128</v>
+        <v>185.4163512192127</v>
       </c>
       <c r="U79" s="149" t="n">
         <v>192.8688330754495</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>210.4858855252497</v>
+        <v>210.4858855252496</v>
       </c>
       <c r="W79" s="149" t="n">
         <v>214.0047110961131</v>
@@ -8325,10 +8325,10 @@
         <v>228.9165257908192</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>167.2084765546757</v>
+        <v>167.2084765546756</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>136.2511309228391</v>
+        <v>136.251130922839</v>
       </c>
       <c r="AA79" s="149" t="n">
         <v>119.2521612710272</v>
@@ -8340,19 +8340,19 @@
         <v>108.9058607753762</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>26341.16222734955</v>
+        <v>26341.16222734954</v>
       </c>
       <c r="AE79" s="152" t="n">
         <v>25006.80944039012</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>26644.06184234361</v>
+        <v>26644.0618423436</v>
       </c>
       <c r="AG79" s="152" t="n">
         <v>26043.40209844784</v>
       </c>
       <c r="AH79" s="153" t="n">
-        <v>26381.08666915488</v>
+        <v>26381.08666915487</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
@@ -8371,13 +8371,13 @@
         <v>311.4000205947125</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>347.3623777653925</v>
+        <v>347.3623777653924</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>373.3680918579745</v>
+        <v>373.3680918579744</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>206.5575802734972</v>
+        <v>206.5575802734971</v>
       </c>
       <c r="I80" s="156" t="n">
         <v>171.3234454341575</v>
@@ -8386,13 +8386,13 @@
         <v>171.5625909330092</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>186.9412604717898</v>
+        <v>186.9412604717897</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>197.8360289087525</v>
+        <v>197.8360289087524</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>22432.76645581946</v>
+        <v>22432.76645581945</v>
       </c>
       <c r="N80" s="159" t="n">
         <v>22124.62439179996</v>
@@ -8401,10 +8401,10 @@
         <v>25686.67107992767</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>29822.05807506683</v>
+        <v>29822.05807506682</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>33172.06839169404</v>
+        <v>33172.06839169403</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8439,10 +8439,10 @@
         <v>187.6635788199981</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>198.588602145134</v>
+        <v>198.5886021451339</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>22432.76645581946</v>
+        <v>22432.76645581945</v>
       </c>
       <c r="AE80" s="159" t="n">
         <v>22124.62439179996</v>
@@ -8451,10 +8451,10 @@
         <v>25686.67107992767</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>29822.05807506683</v>
+        <v>29822.05807506682</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>33172.06839169404</v>
+        <v>33172.06839169403</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>208.2904035884389</v>
+        <v>208.2904035884388</v>
       </c>
       <c r="D81" s="162" t="n">
         <v>215.133135766275</v>
@@ -8473,10 +8473,10 @@
         <v>239.6916376750332</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>258.1047446488243</v>
+        <v>258.1047446488242</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>280.2321596633729</v>
+        <v>280.2321596633728</v>
       </c>
       <c r="H81" s="161" t="n">
         <v>176.3825695666051</v>
@@ -8491,10 +8491,10 @@
         <v>138.4437516575337</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>142.3568990204986</v>
+        <v>142.3568990204985</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>48773.92868316901</v>
+        <v>48773.928683169</v>
       </c>
       <c r="N81" s="165" t="n">
         <v>47131.43383219007</v>
@@ -8503,10 +8503,10 @@
         <v>52330.73292227127</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>55865.46017351467</v>
+        <v>55865.46017351466</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>59553.15506084892</v>
+        <v>59553.15506084891</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,22 +8514,22 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>218.5280349972388</v>
+        <v>218.5280349972387</v>
       </c>
       <c r="U81" s="162" t="n">
         <v>225.4769661849485</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>251.0091789470309</v>
+        <v>251.0091789470308</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>269.9671137930005</v>
+        <v>269.9671137930004</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>292.7116381758752</v>
+        <v>292.7116381758751</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>183.6689959999333</v>
+        <v>183.6689959999332</v>
       </c>
       <c r="Z81" s="162" t="n">
         <v>151.012709163445</v>
@@ -8544,7 +8544,7 @@
         <v>145.5083081129054</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>48773.92868316901</v>
+        <v>48773.928683169</v>
       </c>
       <c r="AE81" s="165" t="n">
         <v>47131.43383219007</v>
@@ -8553,10 +8553,10 @@
         <v>52330.73292227127</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>55865.46017351467</v>
+        <v>55865.46017351466</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>59553.15506084892</v>
+        <v>59553.15506084891</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8593,7 +8593,7 @@
         <v>568.2731845328248</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>590.3522304168397</v>
+        <v>590.3522304168398</v>
       </c>
       <c r="M82" s="158" t="n">
         <v>44356.23568128437</v>
@@ -8608,7 +8608,7 @@
         <v>77876.15922685125</v>
       </c>
       <c r="Q82" s="160" t="n">
-        <v>89797.18623305204</v>
+        <v>89797.18623305205</v>
       </c>
       <c r="S82" s="32" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>641.9251547466953</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>662.2434492821616</v>
+        <v>662.2434492821617</v>
       </c>
       <c r="AD82" s="158" t="n">
         <v>44356.23568128437</v>
@@ -8658,7 +8658,7 @@
         <v>77876.15922685125</v>
       </c>
       <c r="AH82" s="160" t="n">
-        <v>89797.18623305204</v>
+        <v>89797.18623305205</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" thickTop="1">
@@ -8680,7 +8680,7 @@
         <v>450.149436924251</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>502.4893591307165</v>
+        <v>502.4893591307167</v>
       </c>
       <c r="H83" s="161" t="n">
         <v>252.1239159319129</v>
@@ -8689,7 +8689,7 @@
         <v>228.2162985045395</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>226.1352310186982</v>
+        <v>226.1352310186981</v>
       </c>
       <c r="K83" s="162" t="n">
         <v>247.410979808902</v>
@@ -8710,7 +8710,7 @@
         <v>133741.6194003659</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>149350.3412939009</v>
+        <v>149350.341293901</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8730,22 +8730,22 @@
         <v>491.9306112273324</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>549.7932124557775</v>
+        <v>549.7932124557776</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>271.1212036281479</v>
+        <v>271.121203628148</v>
       </c>
       <c r="Z83" s="162" t="n">
         <v>242.6296075904888</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>238.2573442641596</v>
+        <v>238.2573442641595</v>
       </c>
       <c r="AB83" s="162" t="n">
         <v>259.5258765978517</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>274.1016511784578</v>
+        <v>274.1016511784579</v>
       </c>
       <c r="AD83" s="164" t="n">
         <v>93130.16436445338</v>
@@ -8760,7 +8760,7 @@
         <v>133741.6194003659</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>149350.3412939009</v>
+        <v>149350.341293901</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8773,43 +8773,43 @@
         <v>251.8246595737656</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>379.7415776342887</v>
+        <v>379.7415776342885</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>413.7600915489919</v>
+        <v>413.7600915489917</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>445.4766989390283</v>
+        <v>445.4766989390282</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>478.5997687531333</v>
+        <v>478.5997687531332</v>
       </c>
       <c r="H84" s="155" t="n">
         <v>251.8246595737656</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>379.7415776342887</v>
+        <v>379.7415776342885</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>413.7600915489919</v>
+        <v>413.7600915489917</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>445.4766989390283</v>
+        <v>445.4766989390282</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>478.5997687531333</v>
+        <v>478.5997687531331</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>755.2092654082581</v>
+        <v>755.209265408258</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>843.30953446993</v>
+        <v>843.3095344699298</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>946.779692542145</v>
+        <v>946.7796925421447</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>1040.027194855269</v>
+        <v>1040.027194855268</v>
       </c>
       <c r="Q84" s="160" t="n">
         <v>1140.017687397478</v>
@@ -8820,46 +8820,46 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>41.97077659562761</v>
+        <v>41.9707765956276</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>63.29026293904812</v>
+        <v>63.29026293904809</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>68.96001525816531</v>
+        <v>68.9600152581653</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>74.24611648983806</v>
+        <v>74.24611648983804</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>79.76662812552223</v>
+        <v>79.7666281255222</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>41.97077659562761</v>
+        <v>41.9707765956276</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>63.29026293904812</v>
+        <v>63.29026293904809</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>68.96001525816531</v>
+        <v>68.9600152581653</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>74.24611648983806</v>
+        <v>74.24611648983804</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>79.76662812552223</v>
+        <v>79.7666281255222</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>755.2092654082581</v>
+        <v>755.209265408258</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>843.30953446993</v>
+        <v>843.3095344699298</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>946.779692542145</v>
+        <v>946.7796925421447</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>1040.027194855269</v>
+        <v>1040.027194855268</v>
       </c>
       <c r="AH84" s="160" t="n">
         <v>1140.017687397478</v>
@@ -8875,7 +8875,7 @@
         <v>299.321183633328</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>329.0122251179391</v>
+        <v>329.012225117939</v>
       </c>
       <c r="E85" s="180" t="n">
         <v>382.802596966913</v>
@@ -8934,7 +8934,7 @@
         <v>471.464399912476</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>526.3002556489804</v>
+        <v>526.3002556489805</v>
       </c>
       <c r="Y85" s="185" t="n">
         <v>259.7150264385089</v>
@@ -8964,7 +8964,7 @@
         <v>134781.6465952212</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>150490.3589812984</v>
+        <v>150490.3589812985</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9771,7 +9771,7 @@
         <v>297.2209034481251</v>
       </c>
       <c r="H94" s="85" t="n">
-        <v>58.72048393034001</v>
+        <v>58.72048393034</v>
       </c>
       <c r="I94" s="86" t="n">
         <v>131.35525567278</v>
@@ -9798,7 +9798,7 @@
         <v>540.5646083438444</v>
       </c>
       <c r="Q94" s="87" t="n">
-        <v>570.4447911558651</v>
+        <v>570.444791155865</v>
       </c>
       <c r="S94" s="42" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>271.6482086542927</v>
       </c>
       <c r="Y94" s="85" t="n">
-        <v>58.72048393034001</v>
+        <v>58.72048393034</v>
       </c>
       <c r="Z94" s="86" t="n">
         <v>131.35525567278</v>
@@ -9880,7 +9880,7 @@
         <v>2.334638820239654</v>
       </c>
       <c r="G95" s="81" t="n">
-        <v>2.381985453874114</v>
+        <v>2.381985453874115</v>
       </c>
       <c r="H95" s="79" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
         <v>2.334638820239654</v>
       </c>
       <c r="Q95" s="81" t="n">
-        <v>2.381985453874114</v>
+        <v>2.381985453874115</v>
       </c>
       <c r="S95" s="32" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>14.00783292143792</v>
       </c>
       <c r="X95" s="81" t="n">
-        <v>14.29191272324468</v>
+        <v>14.29191272324469</v>
       </c>
       <c r="Y95" s="79" t="n">
         <v>0</v>
@@ -9960,7 +9960,7 @@
         <v>14.00783292143792</v>
       </c>
       <c r="AH95" s="81" t="n">
-        <v>14.29191272324468</v>
+        <v>14.29191272324469</v>
       </c>
       <c r="AJ95" s="120" t="n">
         <v>180</v>
@@ -9991,7 +9991,7 @@
         <v>313.660972772553</v>
       </c>
       <c r="D96" s="133" t="n">
-        <v>300.7453812153509</v>
+        <v>300.745381215351</v>
       </c>
       <c r="E96" s="133" t="n">
         <v>302.8121014439594</v>
@@ -10003,7 +10003,7 @@
         <v>299.6028889019992</v>
       </c>
       <c r="H96" s="132" t="n">
-        <v>58.72048393034001</v>
+        <v>58.72048393034</v>
       </c>
       <c r="I96" s="133" t="n">
         <v>131.35525567278</v>
@@ -10053,7 +10053,7 @@
         <v>285.9401213775374</v>
       </c>
       <c r="Y96" s="135" t="n">
-        <v>58.72048393034001</v>
+        <v>58.72048393034</v>
       </c>
       <c r="Z96" s="136" t="n">
         <v>131.35525567278</v>
@@ -10074,7 +10074,7 @@
         <v>417.6675332888115</v>
       </c>
       <c r="AF96" s="136" t="n">
-        <v>496.2768727435289</v>
+        <v>496.2768727435288</v>
       </c>
       <c r="AG96" s="136" t="n">
         <v>529.3384086374205</v>
